--- a/src/views/game/zlzq/cardList/yiersansiwuCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/yiersansiwuCard/z_level.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\keyuanWeb\src\views\game\zlzq\cardList\yiersansiwuCard\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11190" windowHeight="9990" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="10080" windowHeight="10710"/>
   </bookViews>
   <sheets>
     <sheet name="冬神" sheetId="10" r:id="rId1"/>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
   <si>
     <t>名称</t>
   </si>
@@ -44,6 +49,9 @@
     <t>骨爆</t>
   </si>
   <si>
+    <t>噬魂骨妖</t>
+  </si>
+  <si>
     <t>寒风草人</t>
   </si>
   <si>
@@ -65,7 +73,7 @@
     <t>符文·天寒地冻</t>
   </si>
   <si>
-    <t>寒盲刀客</t>
+    <t>符文·武装大军</t>
   </si>
   <si>
     <t>冬幕骑士</t>
@@ -83,9 +91,6 @@
     <t>寒风血刃</t>
   </si>
   <si>
-    <t>不息之灵</t>
-  </si>
-  <si>
     <t>永夜女王</t>
   </si>
   <si>
@@ -104,27 +109,30 @@
     <t>冬神卡等：</t>
   </si>
   <si>
-    <t>心灵黑洞</t>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
   </si>
   <si>
     <t>黑夜突袭</t>
   </si>
   <si>
-    <t>无声攫取</t>
+    <t>黑金勒索者</t>
   </si>
   <si>
     <t>酗酒醉汉</t>
   </si>
   <si>
-    <t>不法交易</t>
+    <t>不法交易1</t>
+  </si>
+  <si>
+    <t>不法交易2</t>
   </si>
   <si>
     <t>海燕精卫</t>
   </si>
   <si>
-    <t>寒夜灯灵</t>
-  </si>
-  <si>
     <t>黑金诈术师</t>
   </si>
   <si>
@@ -161,7 +169,7 @@
     <t>黑松林货郎</t>
   </si>
   <si>
-    <t>寒窗才子</t>
+    <t>深山采药人</t>
   </si>
   <si>
     <t>符文·疾风图腾</t>
@@ -179,13 +187,13 @@
     <t>当铺掌柜</t>
   </si>
   <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
     <t>流岚刃·琳</t>
   </si>
   <si>
     <t>雪域春光·凛</t>
-  </si>
-  <si>
-    <t>三熊阵</t>
   </si>
   <si>
     <t>悟能禅杖</t>
@@ -1182,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1193,7 +1201,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1201,16 +1209,22 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>24</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1"/>
@@ -1218,28 +1232,22 @@
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="1">
-        <f>AVERAGE(C2:C4)</f>
-        <v>21</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>22</v>
-      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>23</v>
+      </c>
+      <c r="D8" s="2"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
@@ -1249,7 +1257,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1260,7 +1268,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1268,10 +1276,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1279,10 +1287,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1293,7 +1301,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1304,13 +1312,19 @@
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1318,26 +1332,20 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2">
-        <f>AVERAGE(C10:C16)</f>
-        <v>20.4285714285714</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="3">
-        <v>3</v>
-      </c>
-      <c r="C22" s="3">
-        <v>18</v>
+      <c r="C20" s="2">
+        <f>AVERAGE(C11:C17)</f>
+        <v>20.1428571428571</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1345,10 +1353,10 @@
         <v>17</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1359,7 +1367,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1370,7 +1378,7 @@
         <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1381,7 +1389,7 @@
         <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1396,14 +1404,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C22:C26)</f>
-        <v>18.8</v>
+        <f>AVERAGE(C23:C26)</f>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1414,8 +1422,8 @@
         <v>23</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C4,C10:C16,C22:C26)</f>
-        <v>20</v>
+        <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
+        <v>21.1333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1454,68 +1462,74 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1"/>
@@ -1523,49 +1537,43 @@
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>18</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2">
-        <v>22</v>
-      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>18.7142857142857</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2">
         <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1580,63 +1588,63 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="2">
-        <f>AVERAGE(C13:C15)</f>
-        <v>17.6666666666667</v>
+        <f>AVERAGE(C14:C15)</f>
+        <v>20.5</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="3">
         <v>2</v>
       </c>
       <c r="C21" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="3">
         <v>3</v>
       </c>
       <c r="C22" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="3">
         <v>4</v>
       </c>
       <c r="C23" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
@@ -1647,13 +1655,13 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1668,14 +1676,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C21:C26)</f>
-        <v>15.5</v>
+        <v>16.8333333333333</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1683,11 +1691,11 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C7,C13:C15,C21:C26)</f>
-        <v>16.9333333333333</v>
+        <f>AVERAGE(C2:C8,C14:C15,C21:C26)</f>
+        <v>18.2</v>
       </c>
     </row>
   </sheetData>
@@ -1720,7 +1728,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1731,62 +1739,62 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -1807,31 +1815,31 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1">
         <f>AVERAGE(C2:C8)</f>
-        <v>16.1428571428571</v>
+        <v>17.2857142857143</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -1842,30 +1850,36 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="2">
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
       </c>
       <c r="C17" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="2">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1873,53 +1887,47 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C14:C17)</f>
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>16</v>
+      </c>
+      <c r="C21" s="2">
+        <f>AVERAGE(C14:C18)</f>
+        <v>14.2</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -1940,14 +1948,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>15</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>16.3333333333333</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1955,11 +1963,11 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C8,C14:C17,C23:C26)</f>
-        <v>15.4</v>
+        <f>AVERAGE(C2:C8,C14:C18,C24:C26)</f>
+        <v>16.0666666666667</v>
       </c>
     </row>
   </sheetData>
